--- a/shared/planilla_mes/planilla_2026-07.xlsx
+++ b/shared/planilla_mes/planilla_2026-07.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U501"/>
+  <dimension ref="A1:U567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -33676,6 +33676,4354 @@
       <c r="T501" s="14" t="n"/>
       <c r="U501" s="15" t="n"/>
     </row>
+    <row r="502">
+      <c r="A502" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B502" s="7" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="C502" s="8" t="inlineStr">
+        <is>
+          <t>GRICEL PAOLA DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="D502" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E502" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F502" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G502" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H502" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L502" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M502" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N502" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O502" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q502" s="12">
+        <f>H502+I502+J502+K502+L502+M502+N502+O502+P502</f>
+        <v/>
+      </c>
+      <c r="R502" s="13" t="n"/>
+      <c r="S502" s="13" t="n"/>
+      <c r="T502" s="14" t="n"/>
+      <c r="U502" s="15" t="n"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B503" s="7" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
+      <c r="C503" s="8" t="inlineStr">
+        <is>
+          <t>GABY REYES JUAREZ</t>
+        </is>
+      </c>
+      <c r="D503" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E503" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F503" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G503" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H503" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I503" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J503" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K503" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L503" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M503" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N503" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O503" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q503" s="12">
+        <f>H503+I503+J503+K503+L503+M503+N503+O503+P503</f>
+        <v/>
+      </c>
+      <c r="R503" s="13" t="n"/>
+      <c r="S503" s="13" t="n"/>
+      <c r="T503" s="14" t="n"/>
+      <c r="U503" s="15" t="n"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="7" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B504" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C504" s="8" t="inlineStr">
+        <is>
+          <t>LILIANA REQUEZ MENDOZA</t>
+        </is>
+      </c>
+      <c r="D504" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E504" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F504" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G504" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K504" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M504" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N504" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O504" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q504" s="12">
+        <f>H504+I504+J504+K504+L504+M504+N504+O504+P504</f>
+        <v/>
+      </c>
+      <c r="R504" s="13" t="n"/>
+      <c r="S504" s="13" t="n"/>
+      <c r="T504" s="14" t="n"/>
+      <c r="U504" s="15" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="7" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B505" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C505" s="8" t="inlineStr">
+        <is>
+          <t>ROQUE GAUDENCIO SALES VEGA</t>
+        </is>
+      </c>
+      <c r="D505" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E505" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F505" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H505" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K505" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N505" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O505" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" s="12">
+        <f>H505+I505+J505+K505+L505+M505+N505+O505+P505</f>
+        <v/>
+      </c>
+      <c r="R505" s="13" t="n"/>
+      <c r="S505" s="13" t="n"/>
+      <c r="T505" s="14" t="n"/>
+      <c r="U505" s="15" t="n"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="7" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B506" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C506" s="8" t="inlineStr">
+        <is>
+          <t>ENRIQUE TRUJILLO LOERA</t>
+        </is>
+      </c>
+      <c r="D506" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E506" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F506" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G506" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H506" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J506" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K506" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L506" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M506" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N506" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O506" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q506" s="12">
+        <f>H506+I506+J506+K506+L506+M506+N506+O506+P506</f>
+        <v/>
+      </c>
+      <c r="R506" s="13" t="n"/>
+      <c r="S506" s="13" t="n"/>
+      <c r="T506" s="14" t="n"/>
+      <c r="U506" s="15" t="n"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B507" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C507" s="8" t="inlineStr">
+        <is>
+          <t>SAORY RAPRAY SILVA</t>
+        </is>
+      </c>
+      <c r="D507" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E507" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F507" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G507" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K507" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L507" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M507" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N507" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="O507" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P507" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" s="12">
+        <f>H507+I507+J507+K507+L507+M507+N507+O507+P507</f>
+        <v/>
+      </c>
+      <c r="R507" s="13" t="n"/>
+      <c r="S507" s="13" t="n"/>
+      <c r="T507" s="14" t="n"/>
+      <c r="U507" s="15" t="n"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B508" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C508" s="8" t="inlineStr"/>
+      <c r="D508" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E508" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F508" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H508" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I508" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K508" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L508" s="10" t="n">
+        <v>283</v>
+      </c>
+      <c r="M508" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N508" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O508" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q508" s="12">
+        <f>H508+I508+J508+K508+L508+M508+N508+O508+P508</f>
+        <v/>
+      </c>
+      <c r="R508" s="13" t="n"/>
+      <c r="S508" s="13" t="n"/>
+      <c r="T508" s="14" t="n"/>
+      <c r="U508" s="15" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="7" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B509" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C509" s="8" t="inlineStr">
+        <is>
+          <t>MIGUEL AMBROSIO COSME</t>
+        </is>
+      </c>
+      <c r="D509" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E509" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F509" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G509" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H509" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I509" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K509" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L509" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M509" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N509" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O509" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q509" s="12">
+        <f>H509+I509+J509+K509+L509+M509+N509+O509+P509</f>
+        <v/>
+      </c>
+      <c r="R509" s="13" t="n"/>
+      <c r="S509" s="13" t="n"/>
+      <c r="T509" s="14" t="n"/>
+      <c r="U509" s="15" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="7" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B510" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C510" s="8" t="inlineStr">
+        <is>
+          <t>NORMA ELVIRA PALMADERA CORAQUILLO</t>
+        </is>
+      </c>
+      <c r="D510" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E510" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F510" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I510" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K510" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M510" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N510" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O510" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P510" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q510" s="12">
+        <f>H510+I510+J510+K510+L510+M510+N510+O510+P510</f>
+        <v/>
+      </c>
+      <c r="R510" s="13" t="n"/>
+      <c r="S510" s="13" t="n"/>
+      <c r="T510" s="14" t="n"/>
+      <c r="U510" s="15" t="n"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B511" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C511" s="8" t="inlineStr">
+        <is>
+          <t>SILVESTRA CATALINA CHAVEZ ESPINOZA</t>
+        </is>
+      </c>
+      <c r="D511" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E511" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F511" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G511" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H511" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K511" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L511" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M511" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N511" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O511" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P511" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q511" s="12">
+        <f>H511+I511+J511+K511+L511+M511+N511+O511+P511</f>
+        <v/>
+      </c>
+      <c r="R511" s="13" t="n"/>
+      <c r="S511" s="13" t="n"/>
+      <c r="T511" s="14" t="n"/>
+      <c r="U511" s="15" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B512" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C512" s="8" t="inlineStr">
+        <is>
+          <t>PRONOEI Y JASS</t>
+        </is>
+      </c>
+      <c r="D512" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E512" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F512" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G512" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H512" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J512" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K512" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L512" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M512" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N512" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O512" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P512" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q512" s="12">
+        <f>H512+I512+J512+K512+L512+M512+N512+O512+P512</f>
+        <v/>
+      </c>
+      <c r="R512" s="13" t="n"/>
+      <c r="S512" s="13" t="n"/>
+      <c r="T512" s="14" t="n"/>
+      <c r="U512" s="15" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B513" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C513" s="8" t="inlineStr">
+        <is>
+          <t>CARMEN PEREZ MONTES</t>
+        </is>
+      </c>
+      <c r="D513" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E513" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F513" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G513" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H513" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I513" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K513" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M513" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N513" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O513" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q513" s="12">
+        <f>H513+I513+J513+K513+L513+M513+N513+O513+P513</f>
+        <v/>
+      </c>
+      <c r="R513" s="13" t="n"/>
+      <c r="S513" s="13" t="n"/>
+      <c r="T513" s="14" t="n"/>
+      <c r="U513" s="15" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B514" s="7" t="inlineStr">
+        <is>
+          <t>29A</t>
+        </is>
+      </c>
+      <c r="C514" s="8" t="inlineStr">
+        <is>
+          <t>EDDY SANTIAGO GARCILAZO TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D514" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E514" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F514" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G514" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J514" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K514" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N514" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O514" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" s="12">
+        <f>H514+I514+J514+K514+L514+M514+N514+O514+P514</f>
+        <v/>
+      </c>
+      <c r="R514" s="13" t="n"/>
+      <c r="S514" s="13" t="n"/>
+      <c r="T514" s="14" t="n"/>
+      <c r="U514" s="15" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B515" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C515" s="8" t="inlineStr">
+        <is>
+          <t>EDWIN AGÜERO TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D515" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E515" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F515" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G515" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H515" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I515" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J515" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K515" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L515" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M515" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N515" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O515" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P515" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q515" s="12">
+        <f>H515+I515+J515+K515+L515+M515+N515+O515+P515</f>
+        <v/>
+      </c>
+      <c r="R515" s="13" t="n"/>
+      <c r="S515" s="13" t="n"/>
+      <c r="T515" s="14" t="n"/>
+      <c r="U515" s="15" t="n"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B516" s="7" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C516" s="8" t="inlineStr">
+        <is>
+          <t>MARILUZ MELGAREJO BEDON</t>
+        </is>
+      </c>
+      <c r="D516" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E516" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F516" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G516" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I516" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J516" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K516" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M516" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N516" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O516" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P516" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q516" s="12">
+        <f>H516+I516+J516+K516+L516+M516+N516+O516+P516</f>
+        <v/>
+      </c>
+      <c r="R516" s="13" t="n"/>
+      <c r="S516" s="13" t="n"/>
+      <c r="T516" s="14" t="n"/>
+      <c r="U516" s="15" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B517" s="7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C517" s="8" t="inlineStr">
+        <is>
+          <t>LUIS MELGAREJO MELENDEZ</t>
+        </is>
+      </c>
+      <c r="D517" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E517" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F517" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J517" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K517" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N517" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q517" s="12">
+        <f>H517+I517+J517+K517+L517+M517+N517+O517+P517</f>
+        <v/>
+      </c>
+      <c r="R517" s="13" t="n"/>
+      <c r="S517" s="13" t="n"/>
+      <c r="T517" s="14" t="n"/>
+      <c r="U517" s="15" t="n"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B518" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C518" s="8" t="inlineStr"/>
+      <c r="D518" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E518" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F518" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G518" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H518" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I518" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J518" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K518" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L518" s="10" t="n">
+        <v>346</v>
+      </c>
+      <c r="M518" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N518" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q518" s="12">
+        <f>H518+I518+J518+K518+L518+M518+N518+O518+P518</f>
+        <v/>
+      </c>
+      <c r="R518" s="13" t="n"/>
+      <c r="S518" s="13" t="n"/>
+      <c r="T518" s="14" t="n"/>
+      <c r="U518" s="15" t="n"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B519" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C519" s="8" t="inlineStr">
+        <is>
+          <t>ADOLFO GUILLERMO JARA TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D519" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E519" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F519" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G519" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H519" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I519" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J519" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K519" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L519" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M519" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N519" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O519" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P519" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q519" s="12">
+        <f>H519+I519+J519+K519+L519+M519+N519+O519+P519</f>
+        <v/>
+      </c>
+      <c r="R519" s="13" t="n"/>
+      <c r="S519" s="13" t="n"/>
+      <c r="T519" s="14" t="n"/>
+      <c r="U519" s="15" t="n"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B520" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C520" s="8" t="inlineStr">
+        <is>
+          <t>FAUSTINO POMA PALLACA</t>
+        </is>
+      </c>
+      <c r="D520" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E520" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F520" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G520" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H520" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I520" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J520" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K520" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L520" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M520" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N520" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O520" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P520" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q520" s="12">
+        <f>H520+I520+J520+K520+L520+M520+N520+O520+P520</f>
+        <v/>
+      </c>
+      <c r="R520" s="13" t="n"/>
+      <c r="S520" s="13" t="n"/>
+      <c r="T520" s="14" t="n"/>
+      <c r="U520" s="15" t="n"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="7" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B521" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C521" s="8" t="inlineStr">
+        <is>
+          <t>RENEE MEDRANO MALLMA</t>
+        </is>
+      </c>
+      <c r="D521" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E521" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F521" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G521" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H521" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I521" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J521" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K521" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L521" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M521" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N521" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O521" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P521" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q521" s="12">
+        <f>H521+I521+J521+K521+L521+M521+N521+O521+P521</f>
+        <v/>
+      </c>
+      <c r="R521" s="13" t="n"/>
+      <c r="S521" s="13" t="n"/>
+      <c r="T521" s="14" t="n"/>
+      <c r="U521" s="15" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="7" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B522" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C522" s="8" t="inlineStr">
+        <is>
+          <t>JUAN ENCARNACION RACACHA</t>
+        </is>
+      </c>
+      <c r="D522" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E522" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F522" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G522" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="K522" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="L522" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M522" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N522" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P522" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q522" s="12">
+        <f>H522+I522+J522+K522+L522+M522+N522+O522+P522</f>
+        <v/>
+      </c>
+      <c r="R522" s="13" t="n"/>
+      <c r="S522" s="13" t="n"/>
+      <c r="T522" s="14" t="n"/>
+      <c r="U522" s="15" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B523" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C523" s="8" t="inlineStr">
+        <is>
+          <t>MELQUIADES SULCA HUAMANI</t>
+        </is>
+      </c>
+      <c r="D523" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E523" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F523" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G523" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I523" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M523" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N523" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O523" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P523" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q523" s="12">
+        <f>H523+I523+J523+K523+L523+M523+N523+O523+P523</f>
+        <v/>
+      </c>
+      <c r="R523" s="13" t="n"/>
+      <c r="S523" s="13" t="n"/>
+      <c r="T523" s="14" t="n"/>
+      <c r="U523" s="15" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="7" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B524" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C524" s="8" t="inlineStr">
+        <is>
+          <t>RUTH LURDINA MILLA CRUZ</t>
+        </is>
+      </c>
+      <c r="D524" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E524" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F524" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G524" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H524" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I524" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K524" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M524" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N524" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O524" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q524" s="12">
+        <f>H524+I524+J524+K524+L524+M524+N524+O524+P524</f>
+        <v/>
+      </c>
+      <c r="R524" s="13" t="n"/>
+      <c r="S524" s="13" t="n"/>
+      <c r="T524" s="14" t="n"/>
+      <c r="U524" s="15" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="7" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B525" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C525" s="8" t="inlineStr">
+        <is>
+          <t>SANTA ANGELICA VALLLADARES DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="D525" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E525" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F525" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K525" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M525" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N525" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O525" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P525" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q525" s="12">
+        <f>H525+I525+J525+K525+L525+M525+N525+O525+P525</f>
+        <v/>
+      </c>
+      <c r="R525" s="13" t="n"/>
+      <c r="S525" s="13" t="n"/>
+      <c r="T525" s="14" t="n"/>
+      <c r="U525" s="15" t="n"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B526" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C526" s="8" t="inlineStr">
+        <is>
+          <t>WILDA CLEOFE ROMERO VALLADARES</t>
+        </is>
+      </c>
+      <c r="D526" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E526" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F526" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N526" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O526" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q526" s="12">
+        <f>H526+I526+J526+K526+L526+M526+N526+O526+P526</f>
+        <v/>
+      </c>
+      <c r="R526" s="13" t="n"/>
+      <c r="S526" s="13" t="n"/>
+      <c r="T526" s="14" t="n"/>
+      <c r="U526" s="15" t="n"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B527" s="7" t="inlineStr">
+        <is>
+          <t>16B</t>
+        </is>
+      </c>
+      <c r="C527" s="8" t="inlineStr">
+        <is>
+          <t>CRESOSTO ALBORNOZ TICLLIO</t>
+        </is>
+      </c>
+      <c r="D527" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E527" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F527" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G527" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K527" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M527" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N527" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O527" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P527" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q527" s="12">
+        <f>H527+I527+J527+K527+L527+M527+N527+O527+P527</f>
+        <v/>
+      </c>
+      <c r="R527" s="13" t="n"/>
+      <c r="S527" s="13" t="n"/>
+      <c r="T527" s="14" t="n"/>
+      <c r="U527" s="15" t="n"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B528" s="7" t="inlineStr">
+        <is>
+          <t>16C</t>
+        </is>
+      </c>
+      <c r="C528" s="8" t="inlineStr">
+        <is>
+          <t>ELOY SIGUEÑAS UGARTE</t>
+        </is>
+      </c>
+      <c r="D528" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E528" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F528" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G528" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H528" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K528" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L528" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M528" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N528" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O528" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P528" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q528" s="12">
+        <f>H528+I528+J528+K528+L528+M528+N528+O528+P528</f>
+        <v/>
+      </c>
+      <c r="R528" s="13" t="n"/>
+      <c r="S528" s="13" t="n"/>
+      <c r="T528" s="14" t="n"/>
+      <c r="U528" s="15" t="n"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B529" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C529" s="8" t="inlineStr">
+        <is>
+          <t>ANTONY JAVIER CRUZ SAMARITANO</t>
+        </is>
+      </c>
+      <c r="D529" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E529" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F529" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G529" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I529" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J529" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K529" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M529" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N529" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O529" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P529" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q529" s="12">
+        <f>H529+I529+J529+K529+L529+M529+N529+O529+P529</f>
+        <v/>
+      </c>
+      <c r="R529" s="13" t="n"/>
+      <c r="S529" s="13" t="n"/>
+      <c r="T529" s="14" t="n"/>
+      <c r="U529" s="15" t="n"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B530" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C530" s="8" t="inlineStr">
+        <is>
+          <t>IESIY BELEN LOPEZ SAMARITANO</t>
+        </is>
+      </c>
+      <c r="D530" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E530" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F530" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G530" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M530" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N530" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O530" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P530" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q530" s="12">
+        <f>H530+I530+J530+K530+L530+M530+N530+O530+P530</f>
+        <v/>
+      </c>
+      <c r="R530" s="13" t="n"/>
+      <c r="S530" s="13" t="n"/>
+      <c r="T530" s="14" t="n"/>
+      <c r="U530" s="15" t="n"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B531" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C531" s="8" t="inlineStr">
+        <is>
+          <t>MARUJA AMALIA SAMARUTANIO</t>
+        </is>
+      </c>
+      <c r="D531" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E531" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F531" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H531" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I531" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K531" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L531" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M531" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N531" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O531" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P531" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q531" s="12">
+        <f>H531+I531+J531+K531+L531+M531+N531+O531+P531</f>
+        <v/>
+      </c>
+      <c r="R531" s="13" t="n"/>
+      <c r="S531" s="13" t="n"/>
+      <c r="T531" s="14" t="n"/>
+      <c r="U531" s="15" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B532" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C532" s="8" t="inlineStr">
+        <is>
+          <t>YOLIT VILLANUEVA ALEGRIA</t>
+        </is>
+      </c>
+      <c r="D532" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E532" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F532" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H532" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I532" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K532" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L532" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M532" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N532" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O532" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P532" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q532" s="12">
+        <f>H532+I532+J532+K532+L532+M532+N532+O532+P532</f>
+        <v/>
+      </c>
+      <c r="R532" s="13" t="n"/>
+      <c r="S532" s="13" t="n"/>
+      <c r="T532" s="14" t="n"/>
+      <c r="U532" s="15" t="n"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B533" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C533" s="8" t="inlineStr">
+        <is>
+          <t>FREDY INGA GAMARA</t>
+        </is>
+      </c>
+      <c r="D533" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E533" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F533" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G533" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H533" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I533" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J533" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K533" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L533" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M533" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N533" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O533" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P533" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q533" s="12">
+        <f>H533+I533+J533+K533+L533+M533+N533+O533+P533</f>
+        <v/>
+      </c>
+      <c r="R533" s="13" t="n"/>
+      <c r="S533" s="13" t="n"/>
+      <c r="T533" s="14" t="n"/>
+      <c r="U533" s="15" t="n"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B534" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C534" s="8" t="inlineStr">
+        <is>
+          <t>LOLA PARIONA LEYVA</t>
+        </is>
+      </c>
+      <c r="D534" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E534" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F534" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G534" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H534" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I534" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J534" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K534" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L534" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M534" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N534" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O534" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P534" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q534" s="12">
+        <f>H534+I534+J534+K534+L534+M534+N534+O534+P534</f>
+        <v/>
+      </c>
+      <c r="R534" s="13" t="n"/>
+      <c r="S534" s="13" t="n"/>
+      <c r="T534" s="14" t="n"/>
+      <c r="U534" s="15" t="n"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B535" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C535" s="8" t="inlineStr">
+        <is>
+          <t>YONY JOSE SAMARITANO HERREDIA</t>
+        </is>
+      </c>
+      <c r="D535" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E535" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F535" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G535" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H535" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I535" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K535" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L535" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M535" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N535" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O535" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P535" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q535" s="12">
+        <f>H535+I535+J535+K535+L535+M535+N535+O535+P535</f>
+        <v/>
+      </c>
+      <c r="R535" s="13" t="n"/>
+      <c r="S535" s="13" t="n"/>
+      <c r="T535" s="14" t="n"/>
+      <c r="U535" s="15" t="n"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B536" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C536" s="8" t="inlineStr">
+        <is>
+          <t>JOSE FRANCISCO SAMARITANO HUAPAYA</t>
+        </is>
+      </c>
+      <c r="D536" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E536" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F536" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G536" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H536" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K536" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L536" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M536" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N536" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O536" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P536" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q536" s="12">
+        <f>H536+I536+J536+K536+L536+M536+N536+O536+P536</f>
+        <v/>
+      </c>
+      <c r="R536" s="13" t="n"/>
+      <c r="S536" s="13" t="n"/>
+      <c r="T536" s="14" t="n"/>
+      <c r="U536" s="15" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B537" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C537" s="8" t="inlineStr">
+        <is>
+          <t>TANIA SAMARITANO HERREDIA</t>
+        </is>
+      </c>
+      <c r="D537" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E537" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F537" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K537" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L537" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N537" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O537" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P537" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q537" s="12">
+        <f>H537+I537+J537+K537+L537+M537+N537+O537+P537</f>
+        <v/>
+      </c>
+      <c r="R537" s="13" t="n"/>
+      <c r="S537" s="13" t="n"/>
+      <c r="T537" s="14" t="n"/>
+      <c r="U537" s="15" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B538" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C538" s="8" t="inlineStr">
+        <is>
+          <t>INOCENTA MILLA BOTELLO</t>
+        </is>
+      </c>
+      <c r="D538" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E538" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F538" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G538" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H538" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I538" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J538" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K538" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L538" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M538" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N538" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O538" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P538" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q538" s="12">
+        <f>H538+I538+J538+K538+L538+M538+N538+O538+P538</f>
+        <v/>
+      </c>
+      <c r="R538" s="13" t="n"/>
+      <c r="S538" s="13" t="n"/>
+      <c r="T538" s="14" t="n"/>
+      <c r="U538" s="15" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B539" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C539" s="8" t="inlineStr">
+        <is>
+          <t>ZENON MARTIN BURGA TORRES</t>
+        </is>
+      </c>
+      <c r="D539" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E539" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F539" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G539" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H539" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I539" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J539" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K539" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L539" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M539" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N539" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O539" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P539" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q539" s="12">
+        <f>H539+I539+J539+K539+L539+M539+N539+O539+P539</f>
+        <v/>
+      </c>
+      <c r="R539" s="13" t="n"/>
+      <c r="S539" s="13" t="n"/>
+      <c r="T539" s="14" t="n"/>
+      <c r="U539" s="15" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B540" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C540" s="8" t="inlineStr">
+        <is>
+          <t>NELSON NOE MONTALVO CANO</t>
+        </is>
+      </c>
+      <c r="D540" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E540" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F540" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G540" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H540" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I540" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J540" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K540" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L540" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M540" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N540" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O540" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P540" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q540" s="12">
+        <f>H540+I540+J540+K540+L540+M540+N540+O540+P540</f>
+        <v/>
+      </c>
+      <c r="R540" s="13" t="n"/>
+      <c r="S540" s="13" t="n"/>
+      <c r="T540" s="14" t="n"/>
+      <c r="U540" s="15" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="7" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B541" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C541" s="8" t="inlineStr">
+        <is>
+          <t>JORGE BARBOZA AMANTE</t>
+        </is>
+      </c>
+      <c r="D541" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E541" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F541" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G541" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H541" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K541" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M541" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N541" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O541" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P541" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q541" s="12">
+        <f>H541+I541+J541+K541+L541+M541+N541+O541+P541</f>
+        <v/>
+      </c>
+      <c r="R541" s="13" t="n"/>
+      <c r="S541" s="13" t="n"/>
+      <c r="T541" s="14" t="n"/>
+      <c r="U541" s="15" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="7" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B542" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C542" s="8" t="inlineStr">
+        <is>
+          <t>CAPILLA DEL PUEBLO</t>
+        </is>
+      </c>
+      <c r="D542" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E542" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F542" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G542" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H542" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I542" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J542" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="K542" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L542" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="M542" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N542" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O542" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P542" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q542" s="12">
+        <f>H542+I542+J542+K542+L542+M542+N542+O542+P542</f>
+        <v/>
+      </c>
+      <c r="R542" s="13" t="n"/>
+      <c r="S542" s="13" t="n"/>
+      <c r="T542" s="14" t="n"/>
+      <c r="U542" s="15" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B543" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C543" s="8" t="inlineStr">
+        <is>
+          <t>MATILDE MEZA CASTILLEJO</t>
+        </is>
+      </c>
+      <c r="D543" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E543" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F543" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G543" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H543" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I543" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J543" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K543" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L543" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M543" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N543" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O543" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P543" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q543" s="12">
+        <f>H543+I543+J543+K543+L543+M543+N543+O543+P543</f>
+        <v/>
+      </c>
+      <c r="R543" s="13" t="n"/>
+      <c r="S543" s="13" t="n"/>
+      <c r="T543" s="14" t="n"/>
+      <c r="U543" s="15" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B544" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C544" s="8" t="inlineStr">
+        <is>
+          <t>ROBERTO CARLOS QUISPE ROMAN</t>
+        </is>
+      </c>
+      <c r="D544" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E544" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F544" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G544" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H544" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I544" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K544" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L544" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M544" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N544" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P544" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q544" s="12">
+        <f>H544+I544+J544+K544+L544+M544+N544+O544+P544</f>
+        <v/>
+      </c>
+      <c r="R544" s="13" t="n"/>
+      <c r="S544" s="13" t="n"/>
+      <c r="T544" s="14" t="n"/>
+      <c r="U544" s="15" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B545" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C545" s="8" t="inlineStr">
+        <is>
+          <t>SOSIMO ROJAS TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D545" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E545" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F545" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G545" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H545" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I545" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J545" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K545" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L545" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M545" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N545" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O545" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P545" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q545" s="12">
+        <f>H545+I545+J545+K545+L545+M545+N545+O545+P545</f>
+        <v/>
+      </c>
+      <c r="R545" s="13" t="n"/>
+      <c r="S545" s="13" t="n"/>
+      <c r="T545" s="14" t="n"/>
+      <c r="U545" s="15" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B546" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C546" s="8" t="inlineStr">
+        <is>
+          <t>MAXIMA CARRANZA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D546" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E546" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F546" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G546" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H546" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I546" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J546" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K546" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L546" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M546" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N546" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O546" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P546" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q546" s="12">
+        <f>H546+I546+J546+K546+L546+M546+N546+O546+P546</f>
+        <v/>
+      </c>
+      <c r="R546" s="13" t="n"/>
+      <c r="S546" s="13" t="n"/>
+      <c r="T546" s="14" t="n"/>
+      <c r="U546" s="15" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B547" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C547" s="8" t="inlineStr">
+        <is>
+          <t>MARIANELA ELIZABET RIVERA VITATE</t>
+        </is>
+      </c>
+      <c r="D547" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E547" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F547" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G547" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H547" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I547" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J547" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K547" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L547" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M547" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N547" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O547" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P547" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q547" s="12">
+        <f>H547+I547+J547+K547+L547+M547+N547+O547+P547</f>
+        <v/>
+      </c>
+      <c r="R547" s="13" t="n"/>
+      <c r="S547" s="13" t="n"/>
+      <c r="T547" s="14" t="n"/>
+      <c r="U547" s="15" t="n"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B548" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C548" s="8" t="inlineStr">
+        <is>
+          <t>I.E 20902</t>
+        </is>
+      </c>
+      <c r="D548" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E548" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F548" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G548" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I548" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K548" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L548" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M548" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N548" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P548" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q548" s="12">
+        <f>H548+I548+J548+K548+L548+M548+N548+O548+P548</f>
+        <v/>
+      </c>
+      <c r="R548" s="13" t="n"/>
+      <c r="S548" s="13" t="n"/>
+      <c r="T548" s="14" t="n"/>
+      <c r="U548" s="15" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B549" s="7" t="inlineStr">
+        <is>
+          <t>11-B</t>
+        </is>
+      </c>
+      <c r="C549" s="8" t="inlineStr">
+        <is>
+          <t>GILVERTO CLEVER SANCHEZ MEZA</t>
+        </is>
+      </c>
+      <c r="D549" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E549" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F549" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G549" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J549" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K549" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L549" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M549" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N549" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O549" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P549" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q549" s="12">
+        <f>H549+I549+J549+K549+L549+M549+N549+O549+P549</f>
+        <v/>
+      </c>
+      <c r="R549" s="13" t="n"/>
+      <c r="S549" s="13" t="n"/>
+      <c r="T549" s="14" t="n"/>
+      <c r="U549" s="15" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="7" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B550" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C550" s="8" t="inlineStr">
+        <is>
+          <t>RAUL ROMERO MAYO</t>
+        </is>
+      </c>
+      <c r="D550" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E550" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F550" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G550" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H550" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I550" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J550" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K550" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L550" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M550" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N550" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O550" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P550" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q550" s="12">
+        <f>H550+I550+J550+K550+L550+M550+N550+O550+P550</f>
+        <v/>
+      </c>
+      <c r="R550" s="13" t="n"/>
+      <c r="S550" s="13" t="n"/>
+      <c r="T550" s="14" t="n"/>
+      <c r="U550" s="15" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="7" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B551" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C551" s="8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO TRUJILLO DIAZ</t>
+        </is>
+      </c>
+      <c r="D551" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E551" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F551" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H551" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I551" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K551" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L551" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M551" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N551" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P551" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q551" s="12">
+        <f>H551+I551+J551+K551+L551+M551+N551+O551+P551</f>
+        <v/>
+      </c>
+      <c r="R551" s="13" t="n"/>
+      <c r="S551" s="13" t="n"/>
+      <c r="T551" s="14" t="n"/>
+      <c r="U551" s="15" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="7" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B552" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C552" s="8" t="inlineStr">
+        <is>
+          <t>YONY CELEDONIO CERVANTES</t>
+        </is>
+      </c>
+      <c r="D552" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E552" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F552" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J552" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K552" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L552" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M552" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N552" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O552" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P552" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q552" s="12">
+        <f>H552+I552+J552+K552+L552+M552+N552+O552+P552</f>
+        <v/>
+      </c>
+      <c r="R552" s="13" t="n"/>
+      <c r="S552" s="13" t="n"/>
+      <c r="T552" s="14" t="n"/>
+      <c r="U552" s="15" t="n"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="7" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B553" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C553" s="8" t="inlineStr">
+        <is>
+          <t>BEATRIZ ROMERO VALLADARES</t>
+        </is>
+      </c>
+      <c r="D553" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E553" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F553" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H553" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I553" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J553" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K553" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L553" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M553" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N553" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O553" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P553" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q553" s="12">
+        <f>H553+I553+J553+K553+L553+M553+N553+O553+P553</f>
+        <v/>
+      </c>
+      <c r="R553" s="13" t="n"/>
+      <c r="S553" s="13" t="n"/>
+      <c r="T553" s="14" t="n"/>
+      <c r="U553" s="15" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B554" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C554" s="8" t="inlineStr">
+        <is>
+          <t>ANA ISABEL GARRO ROJAS</t>
+        </is>
+      </c>
+      <c r="D554" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E554" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F554" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G554" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H554" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I554" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J554" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K554" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L554" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M554" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N554" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O554" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P554" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q554" s="12">
+        <f>H554+I554+J554+K554+L554+M554+N554+O554+P554</f>
+        <v/>
+      </c>
+      <c r="R554" s="13" t="n"/>
+      <c r="S554" s="13" t="n"/>
+      <c r="T554" s="14" t="n"/>
+      <c r="U554" s="15" t="n"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B555" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C555" s="8" t="inlineStr">
+        <is>
+          <t>VICTORIA COSME CERNA</t>
+        </is>
+      </c>
+      <c r="D555" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E555" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F555" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G555" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H555" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I555" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J555" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K555" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L555" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M555" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N555" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O555" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P555" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q555" s="12">
+        <f>H555+I555+J555+K555+L555+M555+N555+O555+P555</f>
+        <v/>
+      </c>
+      <c r="R555" s="13" t="n"/>
+      <c r="S555" s="13" t="n"/>
+      <c r="T555" s="14" t="n"/>
+      <c r="U555" s="15" t="n"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B556" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C556" s="8" t="inlineStr">
+        <is>
+          <t>SAMUEL SAMARITANO ROMERO</t>
+        </is>
+      </c>
+      <c r="D556" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E556" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F556" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H556" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I556" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K556" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L556" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M556" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N556" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O556" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P556" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q556" s="12">
+        <f>H556+I556+J556+K556+L556+M556+N556+O556+P556</f>
+        <v/>
+      </c>
+      <c r="R556" s="13" t="n"/>
+      <c r="S556" s="13" t="n"/>
+      <c r="T556" s="14" t="n"/>
+      <c r="U556" s="15" t="n"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B557" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C557" s="8" t="inlineStr">
+        <is>
+          <t>HERMELINDA CHAVEZ ESPINOZA</t>
+        </is>
+      </c>
+      <c r="D557" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E557" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F557" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G557" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H557" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I557" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J557" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K557" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L557" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M557" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N557" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O557" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P557" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q557" s="12">
+        <f>H557+I557+J557+K557+L557+M557+N557+O557+P557</f>
+        <v/>
+      </c>
+      <c r="R557" s="13" t="n"/>
+      <c r="S557" s="13" t="n"/>
+      <c r="T557" s="14" t="n"/>
+      <c r="U557" s="15" t="n"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B558" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C558" s="8" t="inlineStr">
+        <is>
+          <t>JENY JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D558" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E558" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F558" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G558" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H558" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J558" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K558" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L558" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M558" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N558" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O558" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P558" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q558" s="12">
+        <f>H558+I558+J558+K558+L558+M558+N558+O558+P558</f>
+        <v/>
+      </c>
+      <c r="R558" s="13" t="n"/>
+      <c r="S558" s="13" t="n"/>
+      <c r="T558" s="14" t="n"/>
+      <c r="U558" s="15" t="n"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B559" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C559" s="8" t="inlineStr">
+        <is>
+          <t>RUDI JORDANO ROCA SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="D559" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E559" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F559" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G559" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H559" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K559" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M559" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N559" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O559" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P559" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q559" s="12">
+        <f>H559+I559+J559+K559+L559+M559+N559+O559+P559</f>
+        <v/>
+      </c>
+      <c r="R559" s="13" t="n"/>
+      <c r="S559" s="13" t="n"/>
+      <c r="T559" s="14" t="n"/>
+      <c r="U559" s="15" t="n"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B560" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C560" s="8" t="inlineStr">
+        <is>
+          <t>MARIA PASTOR SALES DE CARRASCO</t>
+        </is>
+      </c>
+      <c r="D560" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E560" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F560" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G560" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H560" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J560" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K560" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L560" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M560" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N560" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O560" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P560" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q560" s="12">
+        <f>H560+I560+J560+K560+L560+M560+N560+O560+P560</f>
+        <v/>
+      </c>
+      <c r="R560" s="13" t="n"/>
+      <c r="S560" s="13" t="n"/>
+      <c r="T560" s="14" t="n"/>
+      <c r="U560" s="15" t="n"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B561" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C561" s="8" t="inlineStr">
+        <is>
+          <t>IVAN FILOMENO CHAVEZ DAMAZO</t>
+        </is>
+      </c>
+      <c r="D561" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E561" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F561" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G561" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H561" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I561" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J561" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K561" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L561" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M561" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N561" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O561" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P561" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q561" s="12">
+        <f>H561+I561+J561+K561+L561+M561+N561+O561+P561</f>
+        <v/>
+      </c>
+      <c r="R561" s="13" t="n"/>
+      <c r="S561" s="13" t="n"/>
+      <c r="T561" s="14" t="n"/>
+      <c r="U561" s="15" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B562" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C562" s="8" t="inlineStr">
+        <is>
+          <t>GABBY ALICIA HEREDIA ESPINOZA</t>
+        </is>
+      </c>
+      <c r="D562" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E562" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F562" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G562" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H562" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I562" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J562" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K562" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L562" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M562" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N562" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O562" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P562" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q562" s="12">
+        <f>H562+I562+J562+K562+L562+M562+N562+O562+P562</f>
+        <v/>
+      </c>
+      <c r="R562" s="13" t="n"/>
+      <c r="S562" s="13" t="n"/>
+      <c r="T562" s="14" t="n"/>
+      <c r="U562" s="15" t="n"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B563" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C563" s="8" t="inlineStr">
+        <is>
+          <t>YOLANDA MERCEDES LOZANO MINAYA</t>
+        </is>
+      </c>
+      <c r="D563" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E563" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F563" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H563" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I563" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K563" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L563" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M563" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N563" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O563" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P563" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q563" s="12">
+        <f>H563+I563+J563+K563+L563+M563+N563+O563+P563</f>
+        <v/>
+      </c>
+      <c r="R563" s="13" t="n"/>
+      <c r="S563" s="13" t="n"/>
+      <c r="T563" s="14" t="n"/>
+      <c r="U563" s="15" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B564" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C564" s="8" t="inlineStr">
+        <is>
+          <t>ISENIA YESICA CASTILLO BRONCANO</t>
+        </is>
+      </c>
+      <c r="D564" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E564" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F564" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G564" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I564" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J564" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K564" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M564" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N564" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O564" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P564" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q564" s="12">
+        <f>H564+I564+J564+K564+L564+M564+N564+O564+P564</f>
+        <v/>
+      </c>
+      <c r="R564" s="13" t="n"/>
+      <c r="S564" s="13" t="n"/>
+      <c r="T564" s="14" t="n"/>
+      <c r="U564" s="15" t="n"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="7" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B565" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C565" s="8" t="inlineStr">
+        <is>
+          <t>VASQUEZ HHURTADO ORLANDO</t>
+        </is>
+      </c>
+      <c r="D565" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E565" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F565" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M565" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N565" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O565" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P565" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q565" s="12">
+        <f>H565+I565+J565+K565+L565+M565+N565+O565+P565</f>
+        <v/>
+      </c>
+      <c r="R565" s="13" t="n"/>
+      <c r="S565" s="13" t="n"/>
+      <c r="T565" s="14" t="n"/>
+      <c r="U565" s="15" t="n"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="7" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B566" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C566" s="8" t="inlineStr">
+        <is>
+          <t>ESTHEFANY MAGALY PONTE SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D566" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E566" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F566" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N566" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O566" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P566" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q566" s="12">
+        <f>H566+I566+J566+K566+L566+M566+N566+O566+P566</f>
+        <v/>
+      </c>
+      <c r="R566" s="13" t="n"/>
+      <c r="S566" s="13" t="n"/>
+      <c r="T566" s="14" t="n"/>
+      <c r="U566" s="15" t="n"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="7" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B567" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C567" s="8" t="inlineStr">
+        <is>
+          <t>HERMENIJILDA CONDOR ARTICA</t>
+        </is>
+      </c>
+      <c r="D567" s="7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E567" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F567" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G567" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L567" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M567" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N567" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O567" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P567" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q567" s="12">
+        <f>H567+I567+J567+K567+L567+M567+N567+O567+P567</f>
+        <v/>
+      </c>
+      <c r="R567" s="13" t="n"/>
+      <c r="S567" s="13" t="n"/>
+      <c r="T567" s="14" t="n"/>
+      <c r="U567" s="15" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
